--- a/output/pdf_financials_xlsx/NOU.xlsx
+++ b/output/pdf_financials_xlsx/NOU.xlsx
@@ -1431,22 +1431,22 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>5.322944</v>
+        <v>-3.528296</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>10.879413</v>
+        <v>-5.239937</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6.831065</v>
+        <v>-6.831065</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>17.978</v>
+        <v>-17.978</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>40.29</v>
+        <v>-39.49</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>48.114</v>
+        <v>-47.314</v>
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
@@ -1735,22 +1735,22 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>4.42562</v>
+        <v>-4.42562</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>8.059675</v>
+        <v>-8.059675</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>6.831065</v>
+        <v>-6.831065</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>17.978</v>
+        <v>-17.978</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>39.89</v>
+        <v>-39.89</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>47.714</v>
+        <v>-47.714</v>
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
@@ -1945,22 +1945,22 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>4.42562</v>
+        <v>-4.42562</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>8.059675</v>
+        <v>-8.059675</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>6.831065</v>
+        <v>-6.831065</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>17.978</v>
+        <v>-17.978</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39.89</v>
+        <v>-39.89</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>47.714</v>
+        <v>-47.714</v>
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
@@ -2159,19 +2159,19 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-96.20913</v>
+        <v>96.20913</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-149.253241</v>
+        <v>149.253241</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-227.702167</v>
+        <v>227.702167</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-26.438235</v>
+        <v>26.438235</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-42.892473</v>
+        <v>42.892473</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2231,22 +2231,22 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.322944</v>
+        <v>-3.528296</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>10.879413</v>
+        <v>-5.239937</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6.831065</v>
+        <v>-6.831065</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>17.978</v>
+        <v>-17.978</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>40.29</v>
+        <v>-39.49</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>48.114</v>
+        <v>-47.314</v>
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
@@ -2371,22 +2371,22 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.322944</v>
+        <v>-3.528296</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.372483</v>
+        <v>-4.746867</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>7.555095</v>
+        <v>-6.107035</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>19.18</v>
+        <v>-16.776</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>41.385</v>
+        <v>-38.395</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>52.671</v>
+        <v>-42.757</v>
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
@@ -2523,22 +2523,22 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>16.85766372894398</v>
+        <v>-25.43221997247396</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>25.91810789791692</v>
+        <v>-53.81244087476625</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.9928021841648051</v>
+        <v>-1.012914661939732</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0.8313588560502141</v>
+        <v>-0.8454157331867946</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -3617,22 +3617,22 @@
         <v>9.610175999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.829</v>
+        <v>10.416</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.096</v>
+        <v>11.824</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.983</v>
+        <v>14</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.334</v>
+        <v>6.594</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.01</v>
+        <v>7.71</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.518</v>
+        <v>5.512</v>
       </c>
     </row>
     <row r="49">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -28036,13 +28036,13 @@
         </is>
       </c>
       <c r="N208" s="5" t="n">
-        <v>17.978</v>
+        <v>-17.978</v>
       </c>
       <c r="O208" s="5" t="n">
-        <v>39.89</v>
+        <v>-39.89</v>
       </c>
       <c r="P208" s="5" t="n">
-        <v>47.714</v>
+        <v>-47.714</v>
       </c>
       <c r="Q208" t="inlineStr">
         <is>
@@ -30448,13 +30448,13 @@
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>4.42562</v>
+        <v>-4.42562</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>8.059675</v>
+        <v>-8.059675</v>
       </c>
       <c r="M235" s="5" t="n">
-        <v>6.831065</v>
+        <v>-6.831065</v>
       </c>
       <c r="N235" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NOU.xlsx
+++ b/output/pdf_financials_xlsx/NOU.xlsx
@@ -2687,13 +2687,13 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.794449</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.077445</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>62.355</v>
@@ -2819,13 +2819,13 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.794449</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.077445</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>62.355</v>
@@ -3611,13 +3611,13 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.421543</v>
+        <v>2.627094</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>9.610175999999999</v>
+        <v>5.532731</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>10.416</v>
+        <v>5.896</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>11.824</v>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">

--- a/output/pdf_financials_xlsx/NOU.xlsx
+++ b/output/pdf_financials_xlsx/NOU.xlsx
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.022818</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.49307</v>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.528296</v>
+        <v>-3.505478</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-4.746867</v>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.022818</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0.49307</v>
@@ -24537,7 +24537,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -25265,7 +25269,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -25356,7 +25364,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -26365,7 +26373,11 @@
           <t>Addition to intangible asset</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -30956,7 +30968,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -31047,7 +31063,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
